--- a/tests/fixtures/xlsx-pivots/table-dark-5.xlsx
+++ b/tests/fixtures/xlsx-pivots/table-dark-5.xlsx
@@ -10,6 +10,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -43,9 +46,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="1" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -104,7 +108,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>South</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -113,13 +117,13 @@
         </is>
       </c>
       <c r="C2">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="D2">
-        <v>6646</v>
+        <v>6799</v>
       </c>
       <c r="E2">
-        <v>54</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3">
@@ -134,19 +138,19 @@
         </is>
       </c>
       <c r="C3">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D3">
-        <v>4298.01</v>
+        <v>2066.01</v>
       </c>
       <c r="E3">
-        <v>38</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>West</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -155,13 +159,13 @@
         </is>
       </c>
       <c r="C4">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="D4">
-        <v>3942.02</v>
+        <v>1649.02</v>
       </c>
       <c r="E4">
-        <v>78</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5">
@@ -179,16 +183,16 @@
         <v>2023</v>
       </c>
       <c r="D5">
-        <v>2506.03</v>
+        <v>3500.03</v>
       </c>
       <c r="E5">
-        <v>16</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>South</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -197,13 +201,13 @@
         </is>
       </c>
       <c r="C6">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="D6">
-        <v>9070.04</v>
+        <v>7923.04</v>
       </c>
       <c r="E6">
-        <v>86</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/tests/fixtures/xlsx-pivots/table-dark-5.xlsx
+++ b/tests/fixtures/xlsx-pivots/table-dark-5.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr/>
+  <workbookPr defaultThemeVersion="202300"/>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
   </sheets>
@@ -73,6 +73,321 @@
 </table>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 佈景主題">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="0E2841"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E8E8E8"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="156082"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="E97132"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="196B24"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="0F9ED5"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="A02B93"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="4EA72E"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="467886"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="96607D"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main">
   <dimension ref="A1:E6"/>
